--- a/workshops/resources/projects/Midazolam-PAGE/ProjectConfiguration.xlsx
+++ b/workshops/resources/projects/Midazolam-PAGE/ProjectConfiguration.xlsx
@@ -1,43 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
-  <si>
-    <t xml:space="preserve">parameterIdentificationFile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ParameterIdentification.xlsx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Name of the excel file with parameter identification task definitions. Must be located in the "configurationsFolder"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">esqlabsRVersion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6.0.9005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Version of the esqlabsR package used to create this configuration</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -47,12 +24,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <b/>
     </font>
   </fonts>
   <fills count="2">
@@ -373,11 +350,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C16"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
+    <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Property</t>
@@ -550,95 +527,106 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>dataFolder</t>
+          <t>parameterIdentificationFile</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Data/</t>
+          <t>ParameterIdentification.xlsx</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Path to the folder where experimental data files are located; relative to the location of this file</t>
+          <t>Name of the excel file with parameter identification task definitions. Must be located in the "configurationsFolder"</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>dataFile</t>
+          <t>dataFolder</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Midazolam_obs.xlsx</t>
+          <t>Data/</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Name of the excel file with experimental data. Must be located in the "dataFolder"</t>
+          <t>Path to the folder where experimental data files are located; relative to the location of this file</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>dataImporterConfigurationFile</t>
+          <t>dataFile</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>esqlabs_dataImporter_configuration.xml</t>
+          <t>Midazolam_obs.xlsx</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Name of data importer configuration file in xml format used to load the data. Must be located in the "dataFolder"</t>
+          <t>Name of the excel file with experimental data. Must be located in the "dataFolder"</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>dataImporterConfigurationFile</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>esqlabs_dataImporter_configuration.xml</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Name of data importer configuration file in xml format used to load the data. Must be located in the "dataFolder"</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>outputFolder</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>Results/</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Path to the folder where the results should be saved to; relative to the location of this file</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="s">
-        <v>0</v>
-      </c>
-      <c r="B15" t="s">
-        <v>1</v>
-      </c>
-      <c r="C15" t="s">
-        <v>2</v>
-      </c>
-    </row>
     <row r="16">
-      <c r="A16" t="s">
-        <v>3</v>
-      </c>
-      <c r="B16" t="s">
-        <v>4</v>
-      </c>
-      <c r="C16" t="s">
-        <v>5</v>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>esqlabsRVersion</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>5.6.0.9008</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Version of the esqlabsR package used to create this configuration</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>